--- a/translators/xlsx/tests/sample_wraptext.xlsx
+++ b/translators/xlsx/tests/sample_wraptext.xlsx
@@ -35,13 +35,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="false"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -66,6 +69,11 @@
           <t>Normale</t>
         </is>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>wrapText esplicito a false (stile LibreOffice)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
